--- a/exports/RADICO_full_report.xlsx
+++ b/exports/RADICO_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q63"/>
+  <dimension ref="A1:U63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>7.38</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44579.38541666666</v>
+        <v>44579.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>1155.75</v>
+        <v>1145.05</v>
       </c>
       <c r="I2" t="n">
         <v>1155.005</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K2" t="n">
-        <v>-7.32</v>
+        <v>-8.18</v>
       </c>
       <c r="L2" t="n">
-        <v>7.39</v>
+        <v>8.59</v>
       </c>
       <c r="M2" t="n">
         <v>0.29</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>6.81</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44630.38541666666</v>
+        <v>44630.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>914</v>
+        <v>928</v>
       </c>
       <c r="I3" t="n">
         <v>922.6951613140363</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>50.83333333333334</v>
+        <v>51</v>
       </c>
       <c r="K3" t="n">
-        <v>20.18</v>
+        <v>18.96</v>
       </c>
       <c r="L3" t="n">
         <v>3.4</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>10.23</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44645.55208333334</v>
+        <v>44648.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>895.8</v>
+        <v>880.35</v>
       </c>
       <c r="I4" t="n">
         <v>886.4167096324236</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>15</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.47</v>
+        <v>-5.13</v>
       </c>
       <c r="L4" t="n">
         <v>5.71</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>8.74</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44697.38541666666</v>
+        <v>44697.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>800.25</v>
+        <v>829.3</v>
       </c>
       <c r="I5" t="n">
         <v>820.1204474428808</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>49</v>
+        <v>49.16666666666666</v>
       </c>
       <c r="K5" t="n">
-        <v>9.1</v>
+        <v>5.8</v>
       </c>
       <c r="L5" t="n">
         <v>6.32</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>13.02</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44775.55208333334</v>
+        <v>44776.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>934</v>
+        <v>919.8</v>
       </c>
       <c r="I6" t="n">
         <v>923.3793275506652</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>78</v>
+        <v>78.83333333333333</v>
       </c>
       <c r="K6" t="n">
-        <v>12.63</v>
+        <v>10.91</v>
       </c>
       <c r="L6" t="n">
         <v>7.72</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>113</v>
+        <v>114</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>6.15</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44791.38541666666</v>
+        <v>44791.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>958.15</v>
+        <v>962.5</v>
       </c>
       <c r="I7" t="n">
         <v>959.5509669566453</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.17</v>
+        <v>-4.64</v>
       </c>
       <c r="L7" t="n">
         <v>5.43</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>5.71</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44823.38541666666</v>
+        <v>44823.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>1063</v>
+        <v>1047</v>
       </c>
       <c r="I8" t="n">
         <v>1050.120828819599</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>31.83333333333333</v>
+        <v>32</v>
       </c>
       <c r="K8" t="n">
-        <v>10.44</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="L8" t="n">
         <v>2.06</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>8.300000000000001</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44886.55208333334</v>
+        <v>44887.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>1019.95</v>
+        <v>1023.75</v>
       </c>
       <c r="I9" t="n">
         <v>1021.917956995815</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>63</v>
+        <v>63.83333333333334</v>
       </c>
       <c r="K9" t="n">
-        <v>2.58</v>
+        <v>2.22</v>
       </c>
       <c r="L9" t="n">
         <v>8.31</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>8.48</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44915.55208333334</v>
+        <v>44916.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>1057.5</v>
+        <v>1036</v>
       </c>
       <c r="I10" t="n">
         <v>1036.191991356166</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K10" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="L10" t="n">
         <v>2.54</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>6.94</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44931.55208333334</v>
+        <v>44932.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>1013</v>
+        <v>1060.05</v>
       </c>
       <c r="I11" t="n">
         <v>1054.479167430414</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K11" t="n">
-        <v>2.22</v>
+        <v>-2.32</v>
       </c>
       <c r="L11" t="n">
-        <v>2.79</v>
+        <v>3.15</v>
       </c>
       <c r="M11" t="n">
         <v>2.3</v>
       </c>
       <c r="N11" t="n">
-        <v>3.05</v>
+        <v>5.43</v>
       </c>
       <c r="O11" t="n">
         <v>-2.26</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>8.949999999999999</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44949.55208333334</v>
+        <v>44950.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>1043</v>
+        <v>1034.2</v>
       </c>
       <c r="I12" t="n">
         <v>1034.230751052789</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.61</v>
+        <v>-2.44</v>
       </c>
       <c r="L12" t="n">
         <v>4.26</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>5.97</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44953.55208333334</v>
+        <v>44956.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>1062.9</v>
+        <v>1091.75</v>
       </c>
       <c r="I13" t="n">
         <v>1087.9831987454</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.78</v>
+        <v>-5.56</v>
       </c>
       <c r="L13" t="n">
-        <v>3.56</v>
+        <v>6.29</v>
       </c>
       <c r="M13" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="N13" t="n">
-        <v>2.14</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
         <v>-1.25</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>7.49</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44998.55208333334</v>
+        <v>44999.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>1150.05</v>
+        <v>1126.45</v>
       </c>
       <c r="I14" t="n">
         <v>1149.45241396237</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K14" t="n">
-        <v>5.34</v>
+        <v>3.18</v>
       </c>
       <c r="L14" t="n">
         <v>3.24</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>7.68</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45065.38541666666</v>
+        <v>45065.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>1136.2</v>
+        <v>1156</v>
       </c>
       <c r="I15" t="n">
         <v>1147.941341107337</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>66</v>
+        <v>66.16666666666667</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.87</v>
+        <v>-2.62</v>
       </c>
       <c r="L15" t="n">
         <v>8.75</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>5.39</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45142.55208333334</v>
+        <v>45145.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>1370</v>
+        <v>1368.3</v>
       </c>
       <c r="I16" t="n">
         <v>1368.55442384523</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>77</v>
+        <v>79.83333333333333</v>
       </c>
       <c r="K16" t="n">
-        <v>18.51</v>
+        <v>18.37</v>
       </c>
       <c r="L16" t="n">
         <v>5.16</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>109</v>
+        <v>110</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>9.699999999999999</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45210.55208333334</v>
+        <v>45211.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>1228</v>
+        <v>1251.6</v>
       </c>
       <c r="I17" t="n">
         <v>1241.124773971929</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>65.16666666666667</v>
+        <v>66</v>
       </c>
       <c r="K17" t="n">
-        <v>10.25</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="L17" t="n">
         <v>2.61</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>6.36</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45222.38541666666</v>
+        <v>45222.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>1209.6</v>
+        <v>1171</v>
       </c>
       <c r="I18" t="n">
         <v>1200.75710147447</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.36</v>
+        <v>-6.44</v>
       </c>
       <c r="L18" t="n">
-        <v>3.79</v>
+        <v>6.52</v>
       </c>
       <c r="M18" t="n">
         <v>1.43</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>7.46</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45229.38541666666</v>
+        <v>45229.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>1242</v>
+        <v>1253</v>
       </c>
       <c r="I19" t="n">
         <v>1252.872826018361</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K19" t="n">
-        <v>-6.06</v>
+        <v>-7</v>
       </c>
       <c r="L19" t="n">
-        <v>6.65</v>
+        <v>7.05</v>
       </c>
       <c r="M19" t="n">
         <v>1.87</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>6.61</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45268.38541666666</v>
+        <v>45268.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>1574.95</v>
+        <v>1573</v>
       </c>
       <c r="I20" t="n">
         <v>1573.899268318181</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>38.83333333333334</v>
+        <v>39</v>
       </c>
       <c r="K20" t="n">
-        <v>25.69</v>
+        <v>25.54</v>
       </c>
       <c r="L20" t="n">
         <v>3.6</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>9.9</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45289.55208333334</v>
+        <v>45292.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>1662</v>
+        <v>1686</v>
       </c>
       <c r="I21" t="n">
         <v>1683.607383736839</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>21</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="K21" t="n">
-        <v>-5.66</v>
+        <v>-7.18</v>
       </c>
       <c r="L21" t="n">
         <v>9.029999999999999</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>6.27</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45308.55208333334</v>
+        <v>45309.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>1620</v>
+        <v>1599.35</v>
       </c>
       <c r="I22" t="n">
         <v>1609.324471025829</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.91</v>
+        <v>-5.14</v>
       </c>
       <c r="L22" t="n">
-        <v>5.65</v>
+        <v>6.69</v>
       </c>
       <c r="M22" t="n">
         <v>1.2</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>5.74</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45324.55208333334</v>
+        <v>45327.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>1684</v>
+        <v>1739</v>
       </c>
       <c r="I23" t="n">
         <v>1691.156379090899</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K23" t="n">
-        <v>-5.29</v>
+        <v>-8.73</v>
       </c>
       <c r="L23" t="n">
-        <v>5.79</v>
+        <v>13.8</v>
       </c>
       <c r="M23" t="n">
         <v>1.03</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>8</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45343.55208333334</v>
+        <v>45344.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>1658.5</v>
+        <v>1619.7</v>
       </c>
       <c r="I24" t="n">
         <v>1635.564217647812</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K24" t="n">
-        <v>-4.63</v>
+        <v>-6.86</v>
       </c>
       <c r="L24" t="n">
-        <v>5.69</v>
+        <v>7.06</v>
       </c>
       <c r="M24" t="n">
         <v>1.48</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>7.39</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45369.55208333334</v>
+        <v>45370.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>1582.8</v>
+        <v>1620</v>
       </c>
       <c r="I25" t="n">
         <v>1606.600619282143</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K25" t="n">
-        <v>2.28</v>
+        <v>-0.02</v>
       </c>
       <c r="L25" t="n">
         <v>2.92</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>8.949999999999999</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>1752</v>
+        <v>1680.75</v>
       </c>
       <c r="I26" t="n">
         <v>1681.081688138244</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K26" t="n">
-        <v>8.15</v>
+        <v>3.75</v>
       </c>
       <c r="L26" t="n">
         <v>3.2</v>
@@ -1923,7 +2234,7 @@
         <v>0.75</v>
       </c>
       <c r="N26" t="n">
-        <v>2.82</v>
+        <v>2.97</v>
       </c>
       <c r="O26" t="n">
         <v>1.72</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>10.13</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45428.55208333334</v>
+        <v>45429.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>1718.4</v>
+        <v>1733</v>
       </c>
       <c r="I27" t="n">
         <v>1721.761306559164</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.24</v>
+        <v>-3.11</v>
       </c>
       <c r="L27" t="n">
         <v>4.83</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>8.140000000000001</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45441.55208333334</v>
+        <v>45442.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>1605.05</v>
+        <v>1596</v>
       </c>
       <c r="I28" t="n">
         <v>1601.149189880892</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K28" t="n">
-        <v>-7.38</v>
+        <v>-7.91</v>
       </c>
       <c r="L28" t="n">
-        <v>7.38</v>
+        <v>8.31</v>
       </c>
       <c r="M28" t="n">
         <v>0.41</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>5.85</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45447.55208333334</v>
+        <v>45448.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>1569.3</v>
+        <v>1710</v>
       </c>
       <c r="I29" t="n">
         <v>1670.443603537018</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K29" t="n">
-        <v>1.67</v>
+        <v>-7.14</v>
       </c>
       <c r="L29" t="n">
-        <v>2.13</v>
+        <v>7.71</v>
       </c>
       <c r="M29" t="n">
         <v>1.43</v>
       </c>
       <c r="N29" t="n">
-        <v>2.96</v>
+        <v>9.09</v>
       </c>
       <c r="O29" t="n">
         <v>-1.56</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>14.71</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45478.55208333334</v>
+        <v>45481.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>1718</v>
+        <v>1671</v>
       </c>
       <c r="I30" t="n">
         <v>1702.743564392872</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K30" t="n">
-        <v>0.47</v>
+        <v>-2.28</v>
       </c>
       <c r="L30" t="n">
         <v>8.06</v>
@@ -2151,7 +2510,7 @@
         <v>1.11</v>
       </c>
       <c r="N30" t="n">
-        <v>1.84</v>
+        <v>4.6</v>
       </c>
       <c r="O30" t="n">
         <v>9.09</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>7.16</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45525.55208333334</v>
+        <v>45526.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>1720</v>
+        <v>1758.55</v>
       </c>
       <c r="I31" t="n">
         <v>1751.677990295992</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.93</v>
+        <v>-5.24</v>
       </c>
       <c r="L31" t="n">
-        <v>6.89</v>
+        <v>7.48</v>
       </c>
       <c r="M31" t="n">
         <v>5.27</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>6.04</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45562.38541666666</v>
+        <v>45562.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>2110.05</v>
+        <v>2072</v>
       </c>
       <c r="I32" t="n">
         <v>2098.770297024843</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>36</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="K32" t="n">
-        <v>19.99</v>
+        <v>17.82</v>
       </c>
       <c r="L32" t="n">
         <v>1.99</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>8.1</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45579.38541666666</v>
+        <v>45579.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>2139.95</v>
+        <v>2163.8</v>
       </c>
       <c r="I33" t="n">
         <v>2161.747788231669</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>16.83333333333333</v>
+        <v>17</v>
       </c>
       <c r="K33" t="n">
-        <v>-3.28</v>
+        <v>-4.43</v>
       </c>
       <c r="L33" t="n">
-        <v>4.73</v>
+        <v>5.89</v>
       </c>
       <c r="M33" t="n">
         <v>0.9399999999999999</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45610.55208333334</v>
+        <v>45614.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>2243.95</v>
+        <v>2209</v>
       </c>
       <c r="I34" t="n">
         <v>2224.103492182515</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>31</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K34" t="n">
-        <v>3.7</v>
+        <v>2.09</v>
       </c>
       <c r="L34" t="n">
         <v>3.73</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>8.51</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45622.55208333334</v>
+        <v>45623.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>2360</v>
+        <v>2380.6</v>
       </c>
       <c r="I35" t="n">
         <v>2378.172798722522</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K35" t="n">
-        <v>-6.84</v>
+        <v>-7.77</v>
       </c>
       <c r="L35" t="n">
         <v>9.5</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>7.78</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45664.55208333334</v>
+        <v>45665.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>2498</v>
+        <v>2413.5</v>
       </c>
       <c r="I36" t="n">
         <v>2459.123935631477</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K36" t="n">
-        <v>4.93</v>
+        <v>1.38</v>
       </c>
       <c r="L36" t="n">
         <v>2.59</v>
@@ -2493,7 +2924,7 @@
         <v>0.86</v>
       </c>
       <c r="N36" t="n">
-        <v>2.56</v>
+        <v>3.36</v>
       </c>
       <c r="O36" t="n">
         <v>1.27</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>9.460000000000001</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45674.55208333334</v>
+        <v>45677.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>2301</v>
+        <v>2342.6</v>
       </c>
       <c r="I37" t="n">
         <v>2327.847663103046</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K37" t="n">
-        <v>4.66</v>
+        <v>2.94</v>
       </c>
       <c r="L37" t="n">
         <v>4.41</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>9.380000000000001</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45681.55208333334</v>
+        <v>45684.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>2210.1</v>
+        <v>2112.2</v>
       </c>
       <c r="I38" t="n">
         <v>2164.504381720012</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K38" t="n">
-        <v>-5.66</v>
+        <v>-9.84</v>
       </c>
       <c r="L38" t="n">
-        <v>7.7</v>
+        <v>10.78</v>
       </c>
       <c r="M38" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.94</v>
       </c>
       <c r="N38" t="n">
-        <v>3.94</v>
+        <v>4.76</v>
       </c>
       <c r="O38" t="n">
         <v>1.69</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>10.04</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45689.38541666666</v>
+        <v>45689.55208333334</v>
       </c>
       <c r="H39" t="n">
-        <v>2212.55</v>
+        <v>2373.9</v>
       </c>
       <c r="I39" t="n">
         <v>2294.759334953722</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K39" t="n">
-        <v>-4.75</v>
+        <v>-12.39</v>
       </c>
       <c r="L39" t="n">
-        <v>6.2</v>
+        <v>13.74</v>
       </c>
       <c r="M39" t="n">
         <v>1.58</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>13</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>2190</v>
+        <v>2104.95</v>
       </c>
       <c r="I40" t="n">
         <v>2121.658176208346</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K40" t="n">
-        <v>-7.75</v>
+        <v>-11.33</v>
       </c>
       <c r="L40" t="n">
-        <v>8.779999999999999</v>
+        <v>11.79</v>
       </c>
       <c r="M40" t="n">
         <v>0.78</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>11.31</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45707.55208333334</v>
+        <v>45708.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>2018.6</v>
+        <v>2151.15</v>
       </c>
       <c r="I41" t="n">
         <v>2113.288099425456</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K41" t="n">
-        <v>4.1</v>
+        <v>-2.19</v>
       </c>
       <c r="L41" t="n">
         <v>7.58</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>15.65</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45798.38541666666</v>
+        <v>45798.55208333334</v>
       </c>
       <c r="H42" t="n">
-        <v>2449.5</v>
+        <v>2438.9</v>
       </c>
       <c r="I42" t="n">
         <v>2443.849487496679</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>90</v>
+        <v>90.16666666666667</v>
       </c>
       <c r="K42" t="n">
-        <v>13.87</v>
+        <v>13.38</v>
       </c>
       <c r="L42" t="n">
         <v>7.61</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>113</v>
+        <v>114</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>7.09</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45810.55208333334</v>
+        <v>45811.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>2548.1</v>
+        <v>2649</v>
       </c>
       <c r="I43" t="n">
         <v>2579.278840807332</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K43" t="n">
-        <v>-4.48</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="L43" t="n">
-        <v>5.74</v>
+        <v>10.84</v>
       </c>
       <c r="M43" t="n">
-        <v>0.97</v>
+        <v>1.17</v>
       </c>
       <c r="N43" t="n">
-        <v>2.04</v>
+        <v>5.17</v>
       </c>
       <c r="O43" t="n">
         <v>-4.73</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>6.16</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45838.55208333334</v>
+        <v>45839.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>2624.1</v>
+        <v>2570</v>
       </c>
       <c r="I44" t="n">
         <v>2585.066413008587</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-2.98</v>
       </c>
       <c r="L44" t="n">
         <v>4.38</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>6.98</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45846.55208333334</v>
+        <v>45847.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>2636.5</v>
+        <v>2672.8</v>
       </c>
       <c r="I45" t="n">
         <v>2651.549055600454</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K45" t="n">
-        <v>-2.59</v>
+        <v>-4</v>
       </c>
       <c r="L45" t="n">
-        <v>4.01</v>
+        <v>4.09</v>
       </c>
       <c r="M45" t="n">
         <v>0.89</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,25 +3593,25 @@
         <v>5.73</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45905.55208333334</v>
+        <v>45908.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>2799</v>
+        <v>2760.7</v>
       </c>
       <c r="I46" t="n">
         <v>2769.193333351684</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>58.16666666666666</v>
+        <v>61</v>
       </c>
       <c r="K46" t="n">
-        <v>4.72</v>
+        <v>3.29</v>
       </c>
       <c r="L46" t="n">
         <v>3.82</v>
       </c>
       <c r="M46" t="n">
-        <v>0.34</v>
+        <v>0.5</v>
       </c>
       <c r="N46" t="n">
         <v>2.44</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>7.21</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45912.55208333334</v>
+        <v>45915.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>2866.6</v>
+        <v>2942.8</v>
       </c>
       <c r="I47" t="n">
         <v>2902.12119900144</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K47" t="n">
-        <v>-3.84</v>
+        <v>-6.6</v>
       </c>
       <c r="L47" t="n">
-        <v>5.17</v>
+        <v>7.03</v>
       </c>
       <c r="M47" t="n">
-        <v>0.16</v>
+        <v>1.3</v>
       </c>
       <c r="N47" t="n">
-        <v>2.39</v>
+        <v>4.13</v>
       </c>
       <c r="O47" t="n">
         <v>-1.23</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>6.3</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45926.38541666666</v>
+        <v>45926.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>2923.7</v>
+        <v>2893.9</v>
       </c>
       <c r="I48" t="n">
         <v>2909.810468518172</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.65</v>
+        <v>-1.66</v>
       </c>
       <c r="L48" t="n">
-        <v>1.51</v>
+        <v>2.38</v>
       </c>
       <c r="M48" t="n">
         <v>-0</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>5.29</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45946.55208333334</v>
+        <v>45947.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>3003</v>
+        <v>3090</v>
       </c>
       <c r="I49" t="n">
         <v>3016.75620980229</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K49" t="n">
-        <v>-3.77</v>
+        <v>-6.78</v>
       </c>
       <c r="L49" t="n">
-        <v>5.05</v>
+        <v>8.16</v>
       </c>
       <c r="M49" t="n">
         <v>0.75</v>
       </c>
       <c r="N49" t="n">
-        <v>1.93</v>
+        <v>4.06</v>
       </c>
       <c r="O49" t="n">
         <v>-1.9</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>6.18</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45987.55208333334</v>
+        <v>45988.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>3296.8</v>
+        <v>3181.7</v>
       </c>
       <c r="I50" t="n">
         <v>3190.267942076801</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K50" t="n">
-        <v>6.69</v>
+        <v>2.97</v>
       </c>
       <c r="L50" t="n">
         <v>3.03</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>8.35</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46010.55208333334</v>
+        <v>46013.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>3194.1</v>
+        <v>3258.9</v>
       </c>
       <c r="I51" t="n">
         <v>3250.213232830971</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.39</v>
+        <v>-2.43</v>
       </c>
       <c r="L51" t="n">
         <v>3.97</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>7.69</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46023.55208333334</v>
+        <v>46024.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>3257</v>
+        <v>3110.2</v>
       </c>
       <c r="I52" t="n">
         <v>3126.191238519109</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.06</v>
+        <v>-4.56</v>
       </c>
       <c r="L52" t="n">
-        <v>3.34</v>
+        <v>4.76</v>
       </c>
       <c r="M52" t="n">
         <v>1.09</v>
       </c>
       <c r="N52" t="n">
-        <v>2.68</v>
+        <v>5.07</v>
       </c>
       <c r="O52" t="n">
         <v>2.31</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>9.99</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46044.38541666666</v>
+        <v>46044.55208333334</v>
       </c>
       <c r="H53" t="n">
-        <v>2871.4</v>
+        <v>2996</v>
       </c>
       <c r="I53" t="n">
         <v>2973.512156439254</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K53" t="n">
-        <v>7.68</v>
+        <v>3.67</v>
       </c>
       <c r="L53" t="n">
         <v>4.62</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>11.7</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46078.55208333334</v>
+        <v>46079.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>2720</v>
+        <v>2689.4</v>
       </c>
       <c r="I54" t="n">
         <v>2691.264694369766</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>34</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K54" t="n">
-        <v>-9.210000000000001</v>
+        <v>-10.23</v>
       </c>
       <c r="L54" t="n">
-        <v>10.62</v>
+        <v>10.8</v>
       </c>
       <c r="M54" t="n">
         <v>2.05</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>5.11</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46087.38541666666</v>
+        <v>46087.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>2651.9</v>
+        <v>2785</v>
       </c>
       <c r="I55" t="n">
         <v>2708.084280518825</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K55" t="n">
-        <v>1.39</v>
+        <v>-3.55</v>
       </c>
       <c r="L55" t="n">
-        <v>1.32</v>
+        <v>3.89</v>
       </c>
       <c r="M55" t="n">
         <v>1.76</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>10.26</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46099.55208333334</v>
+        <v>46100.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>2720</v>
+        <v>2613.2</v>
       </c>
       <c r="I56" t="n">
         <v>2648.260588620481</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K56" t="n">
-        <v>-2.33</v>
+        <v>-6.17</v>
       </c>
       <c r="L56" t="n">
-        <v>4.87</v>
+        <v>6.36</v>
       </c>
       <c r="M56" t="n">
         <v>1.76</v>
       </c>
       <c r="N56" t="n">
-        <v>2.84</v>
+        <v>4.63</v>
       </c>
       <c r="O56" t="n">
         <v>8.789999999999999</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>10.07</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46122.55208333334</v>
+        <v>46125.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>2785</v>
+        <v>2819.1</v>
       </c>
       <c r="I57" t="n">
         <v>2808.726619265377</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K57" t="n">
-        <v>-6.57</v>
+        <v>-7.88</v>
       </c>
       <c r="L57" t="n">
-        <v>7.57</v>
+        <v>8.02</v>
       </c>
       <c r="M57" t="n">
         <v>2.91</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>8.98</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46262.55208333334</v>
+        <v>46265.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>4615</v>
+        <v>4475.5</v>
       </c>
       <c r="I58" t="n">
         <v>4517.478074270551</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>137.1666666666667</v>
+        <v>140</v>
       </c>
       <c r="K58" t="n">
-        <v>63.7</v>
+        <v>58.76</v>
       </c>
       <c r="L58" t="n">
         <v>3.87</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>192</v>
+        <v>193</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>6</v>
+      </c>
+      <c r="U58" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>5.37</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46287.55208333334</v>
+        <v>46288.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>4458.5</v>
+        <v>4589.9</v>
       </c>
       <c r="I59" t="n">
         <v>4550.96798204517</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K59" t="n">
-        <v>0.38</v>
+        <v>-2.56</v>
       </c>
       <c r="L59" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="M59" t="n">
         <v>0.88</v>
       </c>
       <c r="N59" t="n">
-        <v>2.94</v>
+        <v>3.22</v>
       </c>
       <c r="O59" t="n">
         <v>-3.05</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>6.32</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46295.38541666666</v>
+        <v>46295.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>4430</v>
+        <v>4365.1</v>
       </c>
       <c r="I60" t="n">
         <v>4378.365610820278</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K60" t="n">
-        <v>-3.48</v>
+        <v>-4.9</v>
       </c>
       <c r="L60" t="n">
-        <v>4.36</v>
+        <v>4.9</v>
       </c>
       <c r="M60" t="n">
         <v>0.28</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>5.9</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46300.55208333334</v>
+        <v>46301.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>4285.1</v>
+        <v>4498.8</v>
       </c>
       <c r="I61" t="n">
         <v>4492.531081271307</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K61" t="n">
-        <v>1.83</v>
+        <v>-3.06</v>
       </c>
       <c r="L61" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="M61" t="n">
-        <v>0.03</v>
+        <v>0.35</v>
       </c>
       <c r="N61" t="n">
-        <v>0.72</v>
+        <v>4.34</v>
       </c>
       <c r="O61" t="n">
         <v>-0.6899999999999999</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>7.95</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46314.55208333334</v>
+        <v>46316.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>4449</v>
+        <v>4324.2</v>
       </c>
       <c r="I62" t="n">
         <v>4351.005301824885</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K62" t="n">
-        <v>-1.11</v>
+        <v>-3.88</v>
       </c>
       <c r="L62" t="n">
         <v>4.55</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4035,6 +4790,12 @@
       <c r="Q63" t="n">
         <v>10</v>
       </c>
+      <c r="R63" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6137,7 +6898,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27.5</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="6">
@@ -6147,7 +6908,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -6157,7 +6918,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>137.2</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8">
@@ -6167,7 +6928,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="9">
@@ -6177,7 +6938,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38.8</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
@@ -6187,7 +6948,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="11">
@@ -6227,7 +6988,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.31</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="15">
@@ -6237,7 +6998,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.49</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="16">
@@ -6247,7 +7008,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.06</v>
+        <v>-2.79</v>
       </c>
     </row>
     <row r="17">
@@ -6257,7 +7018,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>63.7</v>
+        <v>58.76</v>
       </c>
     </row>
     <row r="18">
@@ -6267,7 +7028,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45.9</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="19">
@@ -6277,7 +7038,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.02</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="20">
@@ -6287,7 +7048,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.62</v>
+        <v>5.43</v>
       </c>
     </row>
     <row r="21">
@@ -6297,7 +7058,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10.62</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="22">
@@ -6307,7 +7068,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23">
@@ -6317,7 +7078,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -6327,7 +7088,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="25">
@@ -6347,7 +7108,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.85</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="27">
@@ -6367,7 +7128,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29">
